--- a/artfynd/A 25917-2023 artfynd.xlsx
+++ b/artfynd/A 25917-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25917-2023 artfynd.xlsx
+++ b/artfynd/A 25917-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,44 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110712691</v>
+        <v>110712710</v>
       </c>
       <c r="B2" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616227.4861366065</v>
+        <v>616222</v>
       </c>
       <c r="R2" t="n">
-        <v>7268909.847535576</v>
+        <v>7268883</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,19 +746,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,12 +779,7 @@
         <v>110712381</v>
       </c>
       <c r="B3" t="n">
-        <v>90173</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616298.832152246</v>
+        <v>616298</v>
       </c>
       <c r="R3" t="n">
-        <v>7268965.852290165</v>
+        <v>7268966</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,19 +851,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110712759</v>
+        <v>111736268</v>
       </c>
       <c r="B4" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616211.1436908604</v>
+        <v>616309</v>
       </c>
       <c r="R4" t="n">
-        <v>7268850.642596865</v>
+        <v>7268903</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,22 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,12 +985,7 @@
         <v>110712659</v>
       </c>
       <c r="B5" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>616293.9674010263</v>
+        <v>616294</v>
       </c>
       <c r="R5" t="n">
-        <v>7268962.750996395</v>
+        <v>7268963</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1111,19 +1057,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,40 +1087,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111253181</v>
+        <v>110712691</v>
       </c>
       <c r="B6" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1194,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>616402.3138997222</v>
+        <v>616227</v>
       </c>
       <c r="R6" t="n">
-        <v>7268842.09233178</v>
+        <v>7268909</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,19 +1162,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,47 +1192,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111736370</v>
+        <v>111736257</v>
       </c>
       <c r="B7" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1315,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>616327</v>
+        <v>616309</v>
       </c>
       <c r="R7" t="n">
-        <v>7268872</v>
+        <v>7268903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,6 +1274,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1377,37 +1293,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111736268</v>
+        <v>111736405</v>
       </c>
       <c r="B8" t="n">
-        <v>89401</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1420,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>616309</v>
+        <v>616334</v>
       </c>
       <c r="R8" t="n">
-        <v>7268903</v>
+        <v>7268858</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,15 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111736402</v>
+        <v>110712759</v>
       </c>
       <c r="B9" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1526,13 +1432,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>616333</v>
+        <v>616212</v>
       </c>
       <c r="R9" t="n">
-        <v>7268857</v>
+        <v>7268851</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,12 +1462,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,15 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111736257</v>
+        <v>111736370</v>
       </c>
       <c r="B10" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,26 +1506,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1632,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>616309</v>
+        <v>616327</v>
       </c>
       <c r="R10" t="n">
-        <v>7268903</v>
+        <v>7268872</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1582,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1695,15 +1600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111736405</v>
+        <v>111777380</v>
       </c>
       <c r="B11" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,26 +1611,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1738,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>616333</v>
+        <v>616414</v>
       </c>
       <c r="R11" t="n">
-        <v>7268857</v>
+        <v>7268860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,12 +1673,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Skalade stammar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,7 +1692,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1801,47 +1710,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111777380</v>
+        <v>111254922</v>
       </c>
       <c r="B12" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1849,13 +1748,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>616414</v>
+        <v>616420</v>
       </c>
       <c r="R12" t="n">
-        <v>7268860</v>
+        <v>7268585</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1879,17 +1778,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Skalade stammar</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,6 +1792,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1916,37 +1811,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111253338</v>
+        <v>111254964</v>
       </c>
       <c r="B13" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1959,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>616349.8762652914</v>
+        <v>616283</v>
       </c>
       <c r="R13" t="n">
-        <v>7268739.497257653</v>
+        <v>7268705</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,19 +1882,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,15 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111252746</v>
+        <v>111252857</v>
       </c>
       <c r="B14" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,21 +1923,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2075,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>616173.9482352135</v>
+        <v>616276</v>
       </c>
       <c r="R14" t="n">
-        <v>7268647.330667435</v>
+        <v>7268692</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2108,19 +1983,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,15 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111253698</v>
+        <v>111253318</v>
       </c>
       <c r="B15" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,26 +2024,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2191,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>616357.0091243802</v>
+        <v>616357</v>
       </c>
       <c r="R15" t="n">
-        <v>7268571.588119661</v>
+        <v>7268769</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2224,19 +2088,14 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Mycket riktigt apotecier</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,15 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111253092</v>
+        <v>111253338</v>
       </c>
       <c r="B16" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>616339.8834939363</v>
+        <v>616349</v>
       </c>
       <c r="R16" t="n">
-        <v>7268802.219853354</v>
+        <v>7268739</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2340,19 +2194,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,37 +2224,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111253880</v>
+        <v>111253784</v>
       </c>
       <c r="B17" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2423,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>616445.5974736148</v>
+        <v>616400</v>
       </c>
       <c r="R17" t="n">
-        <v>7268674.80549312</v>
+        <v>7268651</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2456,19 +2295,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,42 +2325,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111253147</v>
+        <v>111254260</v>
       </c>
       <c r="B18" t="n">
-        <v>78612</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2539,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>616334.7038700996</v>
+        <v>616654</v>
       </c>
       <c r="R18" t="n">
-        <v>7268817.377759938</v>
+        <v>7268209</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,19 +2400,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,15 +2430,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111252730</v>
+        <v>111254290</v>
       </c>
       <c r="B19" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2628,21 +2441,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2468,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>616160.8644792374</v>
+        <v>616667</v>
       </c>
       <c r="R19" t="n">
-        <v>7268652.20691471</v>
+        <v>7268176</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2688,19 +2501,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,15 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111254201</v>
+        <v>111252730</v>
       </c>
       <c r="B20" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,12 +2551,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2771,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>616481.4461878912</v>
+        <v>616160</v>
       </c>
       <c r="R20" t="n">
-        <v>7268371.399515979</v>
+        <v>7268652</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2804,19 +2602,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,15 +2632,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111254290</v>
+        <v>111254201</v>
       </c>
       <c r="B21" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,21 +2643,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2887,10 +2670,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>616666.8483334343</v>
+        <v>616482</v>
       </c>
       <c r="R21" t="n">
-        <v>7268175.722150465</v>
+        <v>7268371</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2920,19 +2703,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2960,37 +2733,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111254964</v>
+        <v>111252732</v>
       </c>
       <c r="B22" t="n">
-        <v>89646</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3003,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>616283.0432243603</v>
+        <v>616160</v>
       </c>
       <c r="R22" t="n">
-        <v>7268705.678047526</v>
+        <v>7268652</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3036,19 +2804,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,15 +2834,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111253784</v>
+        <v>111252746</v>
       </c>
       <c r="B23" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3092,21 +2845,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3119,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>616400.8149758804</v>
+        <v>616174</v>
       </c>
       <c r="R23" t="n">
-        <v>7268651.002295173</v>
+        <v>7268647</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3152,19 +2905,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,37 +2935,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111254946</v>
+        <v>111777447</v>
       </c>
       <c r="B24" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3235,13 +2973,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>616416.7370724363</v>
+        <v>616380</v>
       </c>
       <c r="R24" t="n">
-        <v>7268575.224019129</v>
+        <v>7268804</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3265,22 +3003,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3308,37 +3036,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111254353</v>
+        <v>111778126</v>
       </c>
       <c r="B25" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3351,13 +3074,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>616748.8137777862</v>
+        <v>616202</v>
       </c>
       <c r="R25" t="n">
-        <v>7268267.897773226</v>
+        <v>7268604</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3381,22 +3104,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3424,37 +3137,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111253794</v>
+        <v>111254193</v>
       </c>
       <c r="B26" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3467,10 +3175,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>616404.4687667027</v>
+        <v>616482</v>
       </c>
       <c r="R26" t="n">
-        <v>7268684.372038134</v>
+        <v>7268371</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3500,19 +3208,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,15 +3238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111252817</v>
+        <v>111253954</v>
       </c>
       <c r="B27" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,21 +3249,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3583,10 +3276,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>616244.7509416816</v>
+        <v>616466</v>
       </c>
       <c r="R27" t="n">
-        <v>7268665.110124372</v>
+        <v>7268676</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3616,19 +3309,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,37 +3339,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111253954</v>
+        <v>111252876</v>
       </c>
       <c r="B28" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3699,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>616466.3363017822</v>
+        <v>616276</v>
       </c>
       <c r="R28" t="n">
-        <v>7268676.051166133</v>
+        <v>7268692</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3732,19 +3410,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3772,37 +3440,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111254040</v>
+        <v>111254229</v>
       </c>
       <c r="B29" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3815,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>616450.0288772837</v>
+        <v>616587</v>
       </c>
       <c r="R29" t="n">
-        <v>7268481.034433298</v>
+        <v>7268300</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3848,19 +3511,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3888,37 +3541,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111254193</v>
+        <v>111254353</v>
       </c>
       <c r="B30" t="n">
-        <v>89419</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3931,10 +3579,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>616481.4461878912</v>
+        <v>616749</v>
       </c>
       <c r="R30" t="n">
-        <v>7268371.399515979</v>
+        <v>7268268</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3964,19 +3612,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4004,15 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111254229</v>
+        <v>111801141</v>
       </c>
       <c r="B31" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4020,21 +3653,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4047,13 +3680,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>616587.4452544958</v>
+        <v>616215</v>
       </c>
       <c r="R31" t="n">
-        <v>7268299.638246101</v>
+        <v>7268648</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4077,22 +3710,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4123,12 +3746,7 @@
         <v>111253627</v>
       </c>
       <c r="B32" t="n">
-        <v>90854</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,10 +3781,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>616367.8880224366</v>
+        <v>616368</v>
       </c>
       <c r="R32" t="n">
-        <v>7268642.624688186</v>
+        <v>7268643</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4196,19 +3814,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4236,15 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111252857</v>
+        <v>111254433</v>
       </c>
       <c r="B33" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4252,21 +3855,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4279,10 +3882,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>616275.2881472342</v>
+        <v>616537</v>
       </c>
       <c r="R33" t="n">
-        <v>7268691.663500885</v>
+        <v>7268509</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4312,19 +3915,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4352,15 +3945,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111254260</v>
+        <v>111777494</v>
       </c>
       <c r="B34" t="n">
-        <v>77186</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4368,30 +3956,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4399,13 +3983,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>616654.3081107945</v>
+        <v>616427</v>
       </c>
       <c r="R34" t="n">
-        <v>7268208.448433449</v>
+        <v>7268746</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4429,22 +4013,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4472,15 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111253213</v>
+        <v>111253599</v>
       </c>
       <c r="B35" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4488,30 +4057,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4519,10 +4084,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>616380.8443888725</v>
+        <v>616339</v>
       </c>
       <c r="R35" t="n">
-        <v>7268796.798990206</v>
+        <v>7268656</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4552,19 +4117,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4592,15 +4147,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111253264</v>
+        <v>111253434</v>
       </c>
       <c r="B36" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,31 +4158,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4640,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>616380.1963899857</v>
+        <v>616352</v>
       </c>
       <c r="R36" t="n">
-        <v>7268781.82311049</v>
+        <v>7268682</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4673,32 +4218,18 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Skalad klen gran</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4717,15 +4248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111253599</v>
+        <v>111253880</v>
       </c>
       <c r="B37" t="n">
-        <v>89330</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,21 +4259,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4760,10 +4286,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>616339.8934839577</v>
+        <v>616446</v>
       </c>
       <c r="R37" t="n">
-        <v>7268656.455437001</v>
+        <v>7268675</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4793,19 +4319,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4833,15 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111254387</v>
+        <v>111777940</v>
       </c>
       <c r="B38" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,31 +4360,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4881,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>616615.1582897741</v>
+        <v>616439</v>
       </c>
       <c r="R38" t="n">
-        <v>7268375.926226165</v>
+        <v>7268804</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4911,22 +4417,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4935,6 +4431,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4953,37 +4450,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111253719</v>
+        <v>111253845</v>
       </c>
       <c r="B39" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4996,10 +4488,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>616371.8042559561</v>
+        <v>616420</v>
       </c>
       <c r="R39" t="n">
-        <v>7268575.917784734</v>
+        <v>7268539</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5029,19 +4521,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5069,37 +4551,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111252623</v>
+        <v>111254946</v>
       </c>
       <c r="B40" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5112,10 +4589,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>616156.5003672343</v>
+        <v>616416</v>
       </c>
       <c r="R40" t="n">
-        <v>7268678.195968762</v>
+        <v>7268576</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5145,19 +4622,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5185,37 +4652,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111252876</v>
+        <v>111778005</v>
       </c>
       <c r="B41" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5228,13 +4690,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>616275.2881472342</v>
+        <v>616499</v>
       </c>
       <c r="R41" t="n">
-        <v>7268691.663500885</v>
+        <v>7268610</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5258,22 +4720,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5301,15 +4753,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111254922</v>
+        <v>111252623</v>
       </c>
       <c r="B42" t="n">
-        <v>89646</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5317,21 +4764,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5344,10 +4791,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>616419.6929341245</v>
+        <v>616157</v>
       </c>
       <c r="R42" t="n">
-        <v>7268584.479073004</v>
+        <v>7268678</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5377,19 +4824,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5417,42 +4854,41 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111254070</v>
+        <v>111253213</v>
       </c>
       <c r="B43" t="n">
-        <v>77268</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5460,10 +4896,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>616467.3814644309</v>
+        <v>616381</v>
       </c>
       <c r="R43" t="n">
-        <v>7268463.039678532</v>
+        <v>7268797</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5493,19 +4929,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5533,47 +4959,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111252609</v>
+        <v>111254011</v>
       </c>
       <c r="B44" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5581,10 +4997,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>616162.9632538864</v>
+        <v>616477</v>
       </c>
       <c r="R44" t="n">
-        <v>7268714.168752246</v>
+        <v>7268730</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5614,32 +5030,18 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Flera skalade klena granar</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5658,15 +5060,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111253652</v>
+        <v>111253698</v>
       </c>
       <c r="B45" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5674,21 +5071,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5701,10 +5098,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>616345.9671296075</v>
+        <v>616357</v>
       </c>
       <c r="R45" t="n">
-        <v>7268577.376012423</v>
+        <v>7268572</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5734,19 +5131,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5774,37 +5161,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>111253434</v>
+        <v>111253794</v>
       </c>
       <c r="B46" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5817,10 +5199,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>616352.5637576731</v>
+        <v>616405</v>
       </c>
       <c r="R46" t="n">
-        <v>7268682.710435705</v>
+        <v>7268684</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5850,19 +5232,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5890,15 +5262,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>111252732</v>
+        <v>111252817</v>
       </c>
       <c r="B47" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5906,21 +5273,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5933,10 +5300,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>616160.8644792374</v>
+        <v>616244</v>
       </c>
       <c r="R47" t="n">
-        <v>7268652.20691471</v>
+        <v>7268666</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5966,19 +5333,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6006,15 +5363,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>111252649</v>
+        <v>111253092</v>
       </c>
       <c r="B48" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6022,31 +5374,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6054,10 +5401,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>616158.7061250493</v>
+        <v>616340</v>
       </c>
       <c r="R48" t="n">
-        <v>7268654.19717967</v>
+        <v>7268802</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6087,27 +5434,18 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6126,37 +5464,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>111253845</v>
+        <v>111253652</v>
       </c>
       <c r="B49" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6169,10 +5502,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>616420.2897608363</v>
+        <v>616346</v>
       </c>
       <c r="R49" t="n">
-        <v>7268538.40363889</v>
+        <v>7268578</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6202,19 +5535,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6242,15 +5565,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>111254433</v>
+        <v>111253685</v>
       </c>
       <c r="B50" t="n">
-        <v>90854</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6258,21 +5576,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6285,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>616536.6424337096</v>
+        <v>616357</v>
       </c>
       <c r="R50" t="n">
-        <v>7268509.007133822</v>
+        <v>7268572</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6318,19 +5636,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6358,15 +5666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>111254011</v>
+        <v>111777499</v>
       </c>
       <c r="B51" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6374,21 +5677,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6401,13 +5704,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>616476.6475364392</v>
+        <v>616427</v>
       </c>
       <c r="R51" t="n">
-        <v>7268730.036465613</v>
+        <v>7268746</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6431,22 +5734,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6474,37 +5767,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>111253685</v>
+        <v>111253147</v>
       </c>
       <c r="B52" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6517,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>616357.0091243802</v>
+        <v>616335</v>
       </c>
       <c r="R52" t="n">
-        <v>7268571.588119661</v>
+        <v>7268817</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6550,19 +5838,9 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2023-07-03</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6590,32 +5868,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>111736506</v>
+        <v>111252649</v>
       </c>
       <c r="B53" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6628,7 +5901,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6638,10 +5911,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>616359</v>
+        <v>616159</v>
       </c>
       <c r="R53" t="n">
-        <v>7268822</v>
+        <v>7268654</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6668,17 +5941,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Födosökande i gransumpskog. Observerades i över en timme</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6705,42 +5973,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>111777447</v>
+        <v>111254387</v>
       </c>
       <c r="B54" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6748,13 +6016,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>616380</v>
+        <v>616616</v>
       </c>
       <c r="R54" t="n">
-        <v>7268804</v>
+        <v>7268376</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6778,12 +6046,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6792,7 +6060,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6811,15 +6078,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>111777491</v>
+        <v>111252609</v>
       </c>
       <c r="B55" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6859,13 +6121,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>616427</v>
+        <v>616163</v>
       </c>
       <c r="R55" t="n">
-        <v>7268746</v>
+        <v>7268714</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6889,17 +6151,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Skalade granstammar</t>
+          <t>Flera skalade klena granar</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6926,15 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>111777494</v>
+        <v>111253264</v>
       </c>
       <c r="B56" t="n">
-        <v>90854</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6942,26 +6199,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6969,13 +6231,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>616427</v>
+        <v>616381</v>
       </c>
       <c r="R56" t="n">
-        <v>7268746</v>
+        <v>7268782</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6999,12 +6261,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Skalad klen gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7013,7 +6280,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7032,42 +6298,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>111777940</v>
+        <v>111736506</v>
       </c>
       <c r="B57" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7075,10 +6341,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>616439</v>
+        <v>616358</v>
       </c>
       <c r="R57" t="n">
-        <v>7268804</v>
+        <v>7268823</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7105,12 +6371,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-08-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Födosökande i gransumpskog. Observerades i över en timme</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7119,7 +6390,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7141,12 +6411,7 @@
         <v>111777411</v>
       </c>
       <c r="B58" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7253,15 +6518,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111778163</v>
+        <v>111777491</v>
       </c>
       <c r="B59" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7301,10 +6561,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>616207</v>
+        <v>616427</v>
       </c>
       <c r="R59" t="n">
-        <v>7268636</v>
+        <v>7268746</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7341,7 +6601,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Skalad gran</t>
+          <t>Skalade granstammar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7368,42 +6628,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111778005</v>
+        <v>111778163</v>
       </c>
       <c r="B60" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7411,10 +6671,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>616499</v>
+        <v>616207</v>
       </c>
       <c r="R60" t="n">
-        <v>7268611</v>
+        <v>7268636</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7449,13 +6709,17 @@
           <t>2023-08-29</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7474,15 +6738,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>111777467</v>
+        <v>111778248</v>
       </c>
       <c r="B61" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7490,26 +6749,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7517,10 +6781,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>616413</v>
+        <v>616163</v>
       </c>
       <c r="R61" t="n">
-        <v>7268760</v>
+        <v>7268630</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7555,13 +6819,17 @@
           <t>2023-08-29</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7580,15 +6848,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>111778126</v>
+        <v>111253719</v>
       </c>
       <c r="B62" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7596,21 +6859,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7623,13 +6886,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>616202</v>
+        <v>616372</v>
       </c>
       <c r="R62" t="n">
-        <v>7268604</v>
+        <v>7268576</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7653,12 +6916,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7686,15 +6949,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>111777499</v>
+        <v>111254040</v>
       </c>
       <c r="B63" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7702,21 +6960,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7729,13 +6987,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>616427</v>
+        <v>616450</v>
       </c>
       <c r="R63" t="n">
-        <v>7268746</v>
+        <v>7268481</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7759,12 +7017,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7792,15 +7050,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>111777331</v>
+        <v>111254070</v>
       </c>
       <c r="B64" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7808,21 +7061,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7835,13 +7088,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>616363</v>
+        <v>616467</v>
       </c>
       <c r="R64" t="n">
-        <v>7268823</v>
+        <v>7268463</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7865,12 +7118,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-07-03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7895,227 +7148,6 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>111778248</v>
-      </c>
-      <c r="B65" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Rankbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>616163</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7268630</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>111801141</v>
-      </c>
-      <c r="B66" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Rankbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>616215</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7268648</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25917-2023 artfynd.xlsx
+++ b/artfynd/A 25917-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110712710</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110712381</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111736268</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110712659</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110712691</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111736257</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111736405</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110712759</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,6 +1642,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111736370</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111777380</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254922</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1909,6 +1969,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254964</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2010,6 +2075,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111252857</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253318</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2221,6 +2296,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253338</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2322,6 +2402,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253784</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2427,6 +2512,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254260</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2528,6 +2618,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254290</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2629,6 +2724,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111252730</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2730,6 +2830,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254201</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2831,6 +2936,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111252732</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2932,6 +3042,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111252746</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3033,6 +3148,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111777447</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3134,6 +3254,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111778126</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3235,6 +3360,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254193</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3336,6 +3466,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253954</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3437,6 +3572,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111252876</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3538,6 +3678,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254229</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3639,6 +3784,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254353</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3740,6 +3890,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111801141</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3841,6 +3996,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253627</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3942,6 +4102,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254433</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4043,6 +4208,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111777494</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4144,6 +4314,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253599</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4245,6 +4420,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253434</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4346,6 +4526,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253880</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4447,6 +4632,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111777940</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4548,6 +4738,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253845</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4649,6 +4844,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254946</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4750,6 +4950,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111778005</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4851,6 +5056,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111252623</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4956,6 +5166,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253213</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5057,6 +5272,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254011</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5158,6 +5378,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253698</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5259,6 +5484,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253794</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5360,6 +5590,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111252817</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5461,6 +5696,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253092</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5562,6 +5802,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253652</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5663,6 +5908,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253685</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5764,6 +6014,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111777499</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5865,6 +6120,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253147</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5970,6 +6230,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111252649</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6075,6 +6340,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254387</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6185,6 +6455,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111252609</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6295,6 +6570,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253264</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6405,6 +6685,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111736506</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6515,6 +6800,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111777411</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6625,6 +6915,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111777491</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6735,6 +7030,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111778163</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6845,6 +7145,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111778248</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6946,6 +7251,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111253719</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7047,6 +7357,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254040</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7148,8 +7463,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111254070</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>